--- a/results/Int Task Remove ACC 0.9/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.9/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0007861031741692894</v>
+        <v>-0.002717807398639028</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.002877241144189429</v>
+        <v>-0.004953765922058545</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001856143209020451</v>
+        <v>-0.001930837799252719</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0003031145774415888</v>
+        <v>-0.0008309891060589615</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0007207550261180684</v>
+        <v>-0.0012036551441919</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.001650068523614705</v>
+        <v>0.001284164556634419</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.119520122433663e-05</v>
+        <v>0.0001266523758062088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005993888196277354</v>
+        <v>-0.001801840604692599</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005957216424155193</v>
+        <v>0.001060471603239539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005625490676237576</v>
+        <v>0.002727346016042766</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0002702709471736842</v>
+        <v>0.00256136149231814</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009005584829259493</v>
+        <v>-0.003551411776344341</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0001818041311764052</v>
+        <v>0.0006122855416819228</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007142718110212491</v>
+        <v>0.006289733653557239</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003215567105819537</v>
+        <v>0.002673878214940642</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001764857318749307</v>
+        <v>0.0001604394485725712</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0001092094964441825</v>
+        <v>-0.001994603309235349</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002157581422622904</v>
+        <v>0.0007180504738875659</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.002465483867965204</v>
+        <v>-0.002831691807378614</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001165932414190485</v>
+        <v>0.0001123865128443091</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001677834820542773</v>
+        <v>0.001580839171685124</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001307968379453915</v>
+        <v>0.0008032181169233278</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0006221738063541471</v>
+        <v>0.0003303794173613161</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001154578133827567</v>
+        <v>0.0003842675417919439</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0003301956814648378</v>
+        <v>0.001229243722574192</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.874024251180448e-06</v>
+        <v>-8.941642536693495e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.001474611857474533</v>
+        <v>-0.0006751391095924143</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.002136360595090122</v>
+        <v>0.000955005394593269</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0008008753414954604</v>
+        <v>0.0008356575715282878</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0006284843481439839</v>
+        <v>-0.0006077004866487589</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0001682893777517024</v>
+        <v>0.0001870352858414603</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0002169323023183767</v>
+        <v>-3.348092790080749e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.001153758316073225</v>
+        <v>0.0009078072611247842</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.001276611573096448</v>
+        <v>-0.0007067617753459243</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.868374574036324e-05</v>
+        <v>8.685516623298862e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002937644806272744</v>
+        <v>-1.678135602145248e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0005027078560454368</v>
+        <v>0.001081146609468675</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0009307877974399038</v>
+        <v>0.0009663708142260542</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0003826418754385741</v>
+        <v>-0.0003628791752656535</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001103696486847259</v>
+        <v>0.0003550074701534899</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.000531604520642317</v>
+        <v>2.544799800421652e-05</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.001110172665992524</v>
+        <v>-0.001800233975860324</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001157406348623667</v>
+        <v>-0.003408666290907926</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.004143608652883888</v>
+        <v>-0.004867746208505638</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0007499390484243884</v>
+        <v>-0.0008910633004779378</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.003256091306806974</v>
+        <v>-0.001376126947035825</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.000240398297317701</v>
+        <v>5.446156854218785e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.00153957487424481</v>
+        <v>-0.001107180243778589</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0006691591544608134</v>
+        <v>-0.002965941348009845</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.0005087705683701894</v>
+        <v>-0.0039994712960632</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.002404506639843229</v>
+        <v>-0.005218125930235561</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0001521697187884973</v>
+        <v>3.458180175061075e-06</v>
       </c>
       <c r="BD3" t="n">
-        <v>-1.977439880839536e-05</v>
+        <v>-0.0003291945808545028</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0002077751548768104</v>
+        <v>-0.001541063494295007</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0006394908898598063</v>
+        <v>-0.004528660573625408</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001583356269188901</v>
+        <v>-0.002135982286338747</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0001676084439328229</v>
+        <v>-3.083659053397803e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0004452537254952538</v>
+        <v>0.0002884561544131758</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002911022319833694</v>
+        <v>-0.001630779764987054</v>
       </c>
       <c r="BL3" t="n">
-        <v>-2.334278241019062e-05</v>
+        <v>3.680086117536784e-06</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.003216746003163126</v>
+        <v>0.0003049461448739455</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.002911724744755906</v>
+        <v>-0.002137444665732796</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.002794983180279721</v>
+        <v>-0.004617609694123333</v>
       </c>
       <c r="BP3" t="n">
-        <v>-4.568829291324075e-05</v>
+        <v>0.0005094214050587219</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.542149858620001e-05</v>
+        <v>5.527825212009451e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0004086037008344912</v>
+        <v>-0.0004756338016406104</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0004705509718981471</v>
+        <v>0.0001752095189144276</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0002541210982602215</v>
+        <v>-0.0001821501554438998</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.001230740026079284</v>
+        <v>-0.0001493926949627522</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001276809619805525</v>
+        <v>-0.0006517233287433754</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0014930450650119</v>
+        <v>0.001061424794926972</v>
       </c>
       <c r="BX3" t="n">
-        <v>3.112739797231589e-05</v>
+        <v>3.205113996645359e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0002576233224963476</v>
+        <v>9.855304449043144e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0002737451860812179</v>
+        <v>0.0003056519396050594</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001197982631544559</v>
+        <v>9.943187700674262e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0002515233250512483</v>
+        <v>0.002261835468085729</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0001763650721575538</v>
+        <v>2.419960195318648e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003924928358525203</v>
+        <v>-0.0005189982594898158</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0001074280331205457</v>
+        <v>0.0003910112393151066</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002735977243660692</v>
+        <v>0.0002661939884183684</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.001638759374015703</v>
+        <v>0.0006964420962749473</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0009125123336911456</v>
+        <v>0.000344759779493835</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0004987919412685771</v>
+        <v>-0.0001318312071312467</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006267869776691971</v>
+        <v>0.005596505361704932</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004613925408377179</v>
+        <v>0.005606547750912133</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003717968342869778</v>
+        <v>0.005846234773639556</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001756379851033234</v>
+        <v>0.002177004022209297</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005723948860306433</v>
+        <v>0.004710199119155287</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00531946277843964</v>
+        <v>0.00300073913050761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003125153727793421</v>
+        <v>0.0002570245100276312</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004703092460500327</v>
+        <v>0.003924337037476498</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01304090951895962</v>
+        <v>0.01814457491179599</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01190626384559392</v>
+        <v>0.01786070406325757</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003294711619125467</v>
+        <v>0.004462893016932688</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002111012559767966</v>
+        <v>0.006114777823877001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003983762049285101</v>
+        <v>0.003315895269066279</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01394424541616195</v>
+        <v>0.01711748038977427</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01567142457920288</v>
+        <v>0.01688944146480603</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002621357771204457</v>
+        <v>0.002798268070584046</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003341077849469599</v>
+        <v>0.005323669052771833</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005953787470128918</v>
+        <v>0.004762534150565865</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00883108018210679</v>
+        <v>0.00789585168710097</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002691128116355273</v>
+        <v>0.0001768000994922526</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004531436930796624</v>
+        <v>0.007360834157885261</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002992937811457214</v>
+        <v>0.002306278008454276</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003141455843077428</v>
+        <v>0.002596985389348756</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001751634474545117</v>
+        <v>0.002933841053516204</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004317387673548747</v>
+        <v>0.003608771859151232</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004303278527069349</v>
+        <v>0.0004155387928925179</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0045210068806807</v>
+        <v>0.004239050986195236</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.003465075442386784</v>
+        <v>0.005042240979675531</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004154905257186878</v>
+        <v>0.002860839360982945</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004206867684251049</v>
+        <v>0.003281549563964372</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0008050455979925774</v>
+        <v>0.0003567473955309281</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0009460219652121702</v>
+        <v>0.0004946240872099627</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004225188521052587</v>
+        <v>0.003434091528490299</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.002576844016592683</v>
+        <v>0.00455679512474117</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0002717972570890153</v>
+        <v>0.0002844243948158838</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001061408755015905</v>
+        <v>0.0002443850856935646</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001550929340648857</v>
+        <v>0.005558667944892213</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004487469745458638</v>
+        <v>0.003967561756406569</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0006198378635855481</v>
+        <v>0.0006375803246897414</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003219526899042829</v>
+        <v>0.002654745320513194</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0023706897395472</v>
+        <v>0.002044012852305793</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003292738778835077</v>
+        <v>0.00346724652594182</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.007669953312143665</v>
+        <v>0.01322022061617382</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.008405826115401771</v>
+        <v>0.01241030660141509</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003024733374549658</v>
+        <v>0.005033364868246746</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.008097785551154842</v>
+        <v>0.004149808224773696</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0006609240687247271</v>
+        <v>0.001278697007882935</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.005084375567017333</v>
+        <v>0.004005141588166044</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004259813365165616</v>
+        <v>0.0074994855640207</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004724155168303833</v>
+        <v>0.009818138862584315</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.003968660441367406</v>
+        <v>0.01087296577156845</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0008832067128974657</v>
+        <v>0.0005600500891786541</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0003475024849128508</v>
+        <v>0.001505708322660073</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001928375809907121</v>
+        <v>0.002994582330137169</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00757023217834561</v>
+        <v>0.01299206178906937</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004558285266668363</v>
+        <v>0.00724494816224304</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001149683467259834</v>
+        <v>0.0008163434355104086</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.003989255162193898</v>
+        <v>0.002626334936113999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.00832608851876576</v>
+        <v>0.01042769925762732</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0006977614749783292</v>
+        <v>0.0004847691506247144</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.008072594563185074</v>
+        <v>0.004148524752447523</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.004278354833200991</v>
+        <v>0.009285272145420985</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.01437548800410745</v>
+        <v>0.01480970383787771</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0009970086994923856</v>
+        <v>0.001624404659530125</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.484876898887651e-05</v>
+        <v>7.761792419485545e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00212378315934074</v>
+        <v>0.003177602456915856</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003700816756521364</v>
+        <v>0.002347631228154898</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001223456820980901</v>
+        <v>0.001952791747201876</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003663710542444455</v>
+        <v>0.002597507684313214</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003527328709027784</v>
+        <v>0.001180659224810907</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.004539474790369999</v>
+        <v>0.001997305789584476</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001822813294060544</v>
+        <v>6.374289335713572e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001269220205748939</v>
+        <v>0.0006242210130158912</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0004855675500524292</v>
+        <v>0.0004894595583956042</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0007635062108370223</v>
+        <v>0.0005125961523141704</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001054767684247311</v>
+        <v>0.002597799852048882</v>
       </c>
       <c r="CD4" t="n">
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0006077546468448266</v>
+        <v>0.0006250102339093186</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001323695930076968</v>
+        <v>0.002240760805195001</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002666730771487079</v>
+        <v>0.001608673212293959</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0008618871900425587</v>
+        <v>0.0006824559528393462</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002552584726309513</v>
+        <v>0.003389275434579351</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.002068212901402795</v>
+        <v>0.00274015561519246</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002247409609721928</v>
+        <v>0.004328541044046283</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01694281133083913</v>
+        <v>-0.01480491715660077</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01060240963855421</v>
+        <v>-0.01514648977335538</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.007692307692307676</v>
+        <v>-0.01246987951807231</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002062868369351622</v>
+        <v>-0.003487229862475394</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01341528594334583</v>
+        <v>-0.009397590361445819</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.009209837781266317</v>
+        <v>-0.002268656716417905</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0004749340369394006</v>
+        <v>-5.344735435596215e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.00678781400320686</v>
+        <v>-0.01012048192771088</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0231907894736842</v>
+        <v>-0.04671052631578952</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02028508771929823</v>
+        <v>-0.04139254385964918</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.00713101160862355</v>
+        <v>-0.001719056974459687</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.001611940298507453</v>
+        <v>-0.01548192771084339</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.00698795180722891</v>
+        <v>-0.00507749866381616</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01694499017681727</v>
+        <v>-0.02814341846758345</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.02720470336718333</v>
+        <v>-0.02084446819882416</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.002576754385964897</v>
+        <v>-0.004331140350877227</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007803313735970085</v>
+        <v>-0.01620481927710847</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01255482456140351</v>
+        <v>-0.004989035087719351</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.02244788882950296</v>
+        <v>-0.02314270443613043</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.232862375719183e-05</v>
+        <v>-0.0001046572475144059</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.005756578947368407</v>
+        <v>-0.007949561403508809</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.00219134152859436</v>
+        <v>-0.003975903614457865</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.008442982456140335</v>
+        <v>-0.005263157894736881</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003244374672946071</v>
+        <v>-0.002850877192982481</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.006633771929824539</v>
+        <v>-0.004989035087719318</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0005482456140351033</v>
+        <v>-0.001134328358208925</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01019736842105262</v>
+        <v>-0.008662280701754422</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.004311774461028173</v>
+        <v>-0.005251520176893287</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.008711918760021397</v>
+        <v>-0.003527525387493335</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.007536076964190297</v>
+        <v>-0.006467661691542259</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.002412280701754354</v>
+        <v>-0.000328947368421062</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0008771929824561653</v>
+        <v>-0.000822368421052655</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.005421686746987964</v>
+        <v>-0.004970603955104247</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.001566265060240979</v>
+        <v>-0.009784411276948545</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0006024096385542244</v>
+        <v>-0.000328947368421062</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002779262426509899</v>
+        <v>-0.0005893909626718763</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.001360544217687054</v>
+        <v>-0.005043859649122839</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.00855157669695351</v>
+        <v>-0.007683803206191231</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0004179104477611828</v>
+        <v>-0.001794195250659658</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002040816326530592</v>
+        <v>-0.003234649122807043</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.002672367717797974</v>
+        <v>-0.002565473009086061</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003855421686746963</v>
+        <v>-0.00753012048192776</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01589912280701753</v>
+        <v>-0.03887061403508775</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.01797642436149309</v>
+        <v>-0.02794695481335948</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.006645735217163773</v>
+        <v>-0.008070757324488632</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.02412349555206695</v>
+        <v>-0.009471480900052376</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001870657402458586</v>
+        <v>-0.003289473684210542</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01496598639455781</v>
+        <v>-0.009894969596462088</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.005699208443271819</v>
+        <v>-0.02132675438596495</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.008607456140350878</v>
+        <v>-0.03070175438596494</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.009484649122807009</v>
+        <v>-0.03426535087719301</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.002302631578947345</v>
+        <v>-0.001098901098901139</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0005277044854882007</v>
+        <v>-0.004477611940298487</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.005451866404715089</v>
+        <v>-0.009577603143418434</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02088815789473684</v>
+        <v>-0.03925438596491233</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01030701754385964</v>
+        <v>-0.01990131578947373</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.002686403508771906</v>
+        <v>-0.00202850877192986</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.008948194662480346</v>
+        <v>-0.002946954813359481</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01662212720470337</v>
+        <v>-0.03015350877192984</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.00114457831325302</v>
+        <v>-0.0007127192982456342</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.02543171114599685</v>
+        <v>-0.005808477237048693</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01127739176910744</v>
+        <v>-0.02669956140350881</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.03644400785854612</v>
+        <v>-0.03644400785854611</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.001465201465201438</v>
+        <v>-0.0009320175438596867</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0.0001583113456464336</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.004081632653061207</v>
+        <v>-0.005451866404715078</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.00659340659340657</v>
+        <v>-0.00309430255402744</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001936159079016186</v>
+        <v>-0.004769736842105299</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.00293040293040292</v>
+        <v>-0.004809286898839115</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002993051843933747</v>
+        <v>-0.00279960707269149</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.005402750491159114</v>
+        <v>-0.001465201465201504</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.000240963855421672</v>
+        <v>-5.527915975677145e-05</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.0008433734939759074</v>
+        <v>-0.0007831325301205338</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.001325301204819285</v>
+        <v>-0.0005421686746988286</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0008372579801151026</v>
+        <v>-0.0004819277108434106</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001589912280701744</v>
+        <v>-0.0001807228915662873</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0004934210526315819</v>
+        <v>-0.001315789473684248</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.002946954813359492</v>
+        <v>-0.004145936981757858</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.005756148613291445</v>
+        <v>-0.001824212271973458</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0005482456140351033</v>
+        <v>-0.001096491228070207</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.007020453289110007</v>
+        <v>-0.004440789473684248</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.002930402930402909</v>
+        <v>-0.004919845218352659</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.006025428413488099</v>
+        <v>-0.008955223880596974</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.00111924546134764</v>
+        <v>-0.003415567375055658</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.005325398661422978</v>
+        <v>-0.009280693780605783</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005305359892148043</v>
+        <v>-0.004962410171365381</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001374651772316043</v>
+        <v>-0.001931778839634016</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002152085579366126</v>
+        <v>-0.004119402985074608</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.005597164383126199</v>
+        <v>-0.0006279434850863686</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001478598853813906</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002028379671706726</v>
+        <v>-0.003630527887814156</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002142806052706852</v>
+        <v>-0.0002261107297559239</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001688654353561994</v>
+        <v>-6.024096385546241e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001715249055925178</v>
+        <v>0.0002246898039920814</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002446447157444742</v>
+        <v>-0.006905243519245902</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002660947680244344</v>
+        <v>-0.001212935855197556</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0008804621470958451</v>
+        <v>-0.00136054166916422</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.001921198755562611</v>
+        <v>-0.003674218432157758</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002166846806751971</v>
+        <v>-0.00104545374454518</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.001368159203980093</v>
+        <v>-0.001139369117473324</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0006903965407326573</v>
+        <v>-0.002211591149985734</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.002813266675924656</v>
+        <v>-0.003392236771779833</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0006963791411728453</v>
+        <v>-0.0007096475099727829</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0004843619596601401</v>
+        <v>-0.0001202565473009232</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001039156626506019</v>
+        <v>-0.0001791993178593104</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0001603420630678865</v>
+        <v>-0.000617098790344603</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.002484939759036142</v>
+        <v>0.0001202565473009093</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0003734545746845952</v>
+        <v>-0.0001367171017468971</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.002559322998026612</v>
+        <v>-0.001533129388745222</v>
       </c>
       <c r="AD6" t="n">
-        <v>-5.943175687825874e-05</v>
+        <v>-0.002191341528594362</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.00195377778303783</v>
+        <v>-0.0008763152875353841</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001043949119836229</v>
+        <v>-0.001643946671665242</v>
       </c>
       <c r="AG6" t="n">
-        <v>-3.924646781789388e-05</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0001351819204352428</v>
+        <v>-0.0003599305939536779</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.0008087661954081782</v>
+        <v>-0.0007578772802653205</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.381978993919286e-05</v>
+        <v>-0.001656867985034743</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0004824382922677756</v>
+        <v>-9.399082147314442e-05</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0007192755189624005</v>
+        <v>-0.002682121650205959</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0006716417910447581</v>
+        <v>-0.0002405130946018297</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>-0.000661986122021474</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-7.915567282324453e-05</v>
+        <v>-0.000458759107458731</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.0002224471388360821</v>
+        <v>-0.001069822391997771</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0009402985074626613</v>
+        <v>-0.004298492801219816</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.002129829658614282</v>
+        <v>-0.0041553747583082</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.00999033416762668</v>
+        <v>-0.009664046351091197</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001313771524788276</v>
+        <v>-0.003406115149262473</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001426332199986191</v>
+        <v>-0.00318493372591504</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0002467105263157965</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.00166862568749318</v>
+        <v>-0.002065014401384346</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.003365171833330166</v>
+        <v>-0.003903423721270335</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.003391256318148595</v>
+        <v>-0.00367468621746101</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.004200861530895961</v>
+        <v>-0.005580431177446074</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0003820790180807554</v>
+        <v>-0.0001583113456464336</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0002259036144578175</v>
+        <v>-0.0001353167882647777</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0.001740943875002499</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.0008059701492537263</v>
+        <v>-0.004913152037780089</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.003775999520469928</v>
+        <v>-0.003936036718552707</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.000332479229294369</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0004353562005277589</v>
+        <v>-0.001226322294579338</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.003539472212672359</v>
+        <v>-0.001005539307626316</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0003968904821783081</v>
+        <v>-0.0002807231035392322</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.003501131360938428</v>
+        <v>-0.001371954949675802</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.005083608438301241</v>
+        <v>-0.001815859651680574</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.00477031359346333</v>
+        <v>-0.003102997237480132</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0008665252040173265</v>
+        <v>-0.0004785090453564511</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>-0.00257664882449741</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0003606365761553737</v>
+        <v>-0.001430846834773222</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>-0.0003576967283815319</v>
       </c>
       <c r="BU6" t="n">
-        <v>-7.915567282325842e-05</v>
+        <v>-0.0005611972207375776</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>-0.001425822223263565</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0.0005611972207375943</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.000309612044297794</v>
+        <v>-0.0002137894174238486</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.000500810095692797</v>
+        <v>5.482456140350755e-05</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-8.017103153394324e-05</v>
+        <v>-4.477611940298387e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>-4.008551576697162e-05</v>
+        <v>0.0005008530658670074</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0</v>
+        <v>-0.0002747252747252904</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0009468290488486659</v>
+        <v>-0.001883502758818467</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0008584337349397648</v>
+        <v>-9.013606537320584e-05</v>
       </c>
       <c r="CH6" t="n">
-        <v>-4.008551576697162e-05</v>
+        <v>4.008551576697161e-05</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002924269637918431</v>
+        <v>-0.0008376005913610263</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.492537313432796e-05</v>
+        <v>-0.0006279434850863853</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0005311985776701667</v>
+        <v>-0.0004709576138147847</v>
       </c>
     </row>
     <row r="7">
@@ -2232,202 +2232,202 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0002878074306645606</v>
+        <v>-0.0008166597732051139</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0008497807017543768</v>
+        <v>-0.003919361657154974</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.847876701610469e-05</v>
+        <v>-0.001999115643461708</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0004407475963979002</v>
+        <v>-0.001057397084190842</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0007574528413342496</v>
+        <v>0.0001090830515137309</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0003724243560391472</v>
+        <v>0.0007465706964655428</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0001145260539408222</v>
+        <v>2.45579567780041e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0004068013346919863</v>
+        <v>-0.0007092762806267638</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008740270008893885</v>
+        <v>0.004919575855668079</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008798048804049829</v>
+        <v>0.006251449563749656</v>
       </c>
       <c r="M7" t="n">
-        <v>6.0240963855418e-05</v>
+        <v>0.0007482629609834146</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004246327909177838</v>
+        <v>-0.002708592047611253</v>
       </c>
       <c r="O7" t="n">
-        <v>5.032028526527621e-05</v>
+        <v>0.001226577953605457</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006306625315136982</v>
+        <v>0.003821485836451077</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001252374543604656</v>
+        <v>0.003158005154948124</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001138374393094754</v>
+        <v>0.0008303548180936149</v>
       </c>
       <c r="S7" t="n">
-        <v>2.985074626865591e-05</v>
+        <v>-0.0008574595018602971</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0031241015659277</v>
+        <v>0.0005066534795899803</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0005671641791044679</v>
+        <v>-0.0002264996662110386</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.26211948174671e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001598054487077555</v>
+        <v>3.039021758675097e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0008579975589715849</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001964636542239939</v>
+        <v>0.0001719056974459954</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001807228915662651</v>
+        <v>2.51586778290569e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.009171012407391e-05</v>
+        <v>0.0008611246280622542</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.616431187860147e-05</v>
+        <v>1.110223024625157e-17</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0008518014778990668</v>
+        <v>0.0004377692490968532</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002174055142129028</v>
+        <v>-0.0008054306779356036</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0009983416252072829</v>
+        <v>0.0001603420630678809</v>
       </c>
       <c r="AF7" t="n">
-        <v>-2.455795677797079e-05</v>
+        <v>-3.384529035754854e-07</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-2.455795677798189e-05</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0001336183858898776</v>
+        <v>-2.672367717798663e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0008551576696953167</v>
+        <v>-0.0006265959359827211</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>2.616431187858481e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001870657402458342</v>
+        <v>0.0003587484265419771</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0001596651572606911</v>
+        <v>0.001302352670745943</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.000388349619136269</v>
+        <v>-0.0002608939231002194</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-4.665374485650632e-05</v>
       </c>
       <c r="AR7" t="n">
+        <v>-0.0002706797893986923</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.001703595384175249</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-4.415846174654072e-05</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.003739510851826683</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0.0003459771152919122</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.0006748855389489828</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.0003300653334077919</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.0002638522427440671</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0.001362907536076968</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.0009790364021559472</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.002613479036402184</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.45579567780152e-05</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-5.551115123125783e-18</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.0003269382643171226</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.0005281306948800302</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.0009421591378707627</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.455795677800965e-05</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0004246327909178005</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.001422891428367418</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-7.849293563581549e-05</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.0001068947087119077</v>
+      </c>
+      <c r="BN7" t="n">
         <v>2.672367717797552e-05</v>
       </c>
-      <c r="AS7" t="n">
-        <v>0.0006389990819464731</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-0.0005421686746988008</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-0.002861445783132527</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.000374131480491724</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-0.0002154590858522432</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-2.672367717798663e-05</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-0.0006146445750935369</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-2.672367717798663e-05</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.00275981569723942</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.974090445894699e-05</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.0005494505494505642</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.0003741314804916962</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-1.110223024625157e-17</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.0002710843373493977</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-0.001288138802755212</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>-5.344735435596215e-05</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>-0.001873480655624165</v>
-      </c>
       <c r="BO7" t="n">
-        <v>-0.0002231706246958787</v>
+        <v>-0.001694093745708658</v>
       </c>
       <c r="BP7" t="n">
         <v>0</v>
@@ -2436,22 +2436,22 @@
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0003304847792698629</v>
+        <v>-0.0002905636442080639</v>
       </c>
       <c r="BS7" t="n">
-        <v>-2.672367717797552e-05</v>
+        <v>-0.0001194029850746237</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002100341665168093</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>9.036144578313255e-05</v>
+        <v>0.0002987806736241938</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0006231244197845542</v>
+        <v>-0.0005033499786351702</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.00045884952575444</v>
+        <v>0.0007149979658096384</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>0.0002906042571614698</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
@@ -2469,31 +2469,31 @@
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001603420630678587</v>
+        <v>0.001095670764297152</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>5.277044854881119e-05</v>
+        <v>0.0001227897838899927</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0004355580215599231</v>
+        <v>0.0001068947087119188</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.000103713629601232</v>
+        <v>0.0004759919015091763</v>
       </c>
       <c r="CH7" t="n">
-        <v>0</v>
+        <v>0.0002636416312014001</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.000409936241703146</v>
+        <v>-0.000187065740245862</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0005547666155696574</v>
+        <v>0.0005285814556998614</v>
       </c>
       <c r="CK7" t="n">
-        <v>-8.017103153394322e-05</v>
+        <v>0.0002436401636925045</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002514882713565478</v>
+        <v>0.0005446323552786237</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000414047769806855</v>
+        <v>0.0002208084073332256</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0006361990200487722</v>
+        <v>0.001995910952256999</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.957783641161949e-05</v>
+        <v>-6.541077969650088e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.036144578314365e-05</v>
+        <v>0.0002909143728255986</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00029021558872305</v>
+        <v>0.001794161532815564</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5.785827534228183e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000853465405177431</v>
+        <v>0.00106037583168494</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01387189298474662</v>
+        <v>0.008601412144692549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01209823237768569</v>
+        <v>0.01459510456079388</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0006738385777080413</v>
+        <v>0.004298647483777237</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001471731252185485</v>
+        <v>0.0001374659514594783</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002043558850787769</v>
+        <v>0.003201828326215803</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01738174046263549</v>
+        <v>0.02046351024190952</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01014436685381655</v>
+        <v>0.007423784849159151</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003296548021812648</v>
+        <v>0.001551133222775023</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001546124437191165</v>
+        <v>0.000170624454701046</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004328414398349514</v>
+        <v>0.001536611437733818</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009950248756218859</v>
+        <v>0.001464422593428866</v>
       </c>
       <c r="V8" t="n">
-        <v>8.017103153394324e-05</v>
+        <v>0.0001570934824679126</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004966283042618216</v>
+        <v>0.004518485541939674</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003821069206181099</v>
+        <v>0.001842287376043866</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00120444199599872</v>
+        <v>0.001096380736616198</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001055015161658695</v>
+        <v>0.0007337603803536985</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009737219524783652</v>
+        <v>0.002068147331999565</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001501072935695458</v>
+        <v>5.265999235090635e-05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001242650988776029</v>
+        <v>0.001409635224146971</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004585682957393499</v>
+        <v>0.003817470769477482</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.0001319261213720446</v>
+        <v>0.002497517892991169</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0001644736842105393</v>
+        <v>0.0004503870097285395</v>
       </c>
       <c r="AG8" t="n">
-        <v>8.70357089229834e-05</v>
+        <v>0.0004575081714770862</v>
       </c>
       <c r="AH8" t="n">
-        <v>9.0361445783127e-05</v>
+        <v>3.957783641160839e-05</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005167490148545478</v>
+        <v>0.003989940931651309</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.001374442100243145</v>
+        <v>0.002173736553683753</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0001243781094527357</v>
+        <v>4.518072289153851e-05</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.111842105263552e-05</v>
+        <v>0.0001170851229611081</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001920708955223896</v>
+        <v>0.002534140273157628</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.004043905886704714</v>
+        <v>0.002549073505781319</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0005121674031217188</v>
+        <v>0.0001343283582089516</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001399049162084343</v>
+        <v>0.0004798331525086075</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0008781176355066923</v>
+        <v>0.0002505390478712011</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002800872373240817</v>
+        <v>0.00156583907471371</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00108230892570815</v>
+        <v>0.00202288866868541</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001567164179104486</v>
+        <v>0.001701492537313454</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001581325301204822</v>
+        <v>0.0004066265060240631</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0004564324289828059</v>
+        <v>0.0006163429774683926</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>0.0005295843962897035</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001355421686746996</v>
+        <v>0.001015356142855986</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.683693516701448e-05</v>
+        <v>0.001006259456326036</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.003536345776031466</v>
+        <v>0.0007607857516233163</v>
       </c>
       <c r="BB8" t="n">
-        <v>-6.680919294495269e-05</v>
+        <v>0.000774084661616134</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0001180010256615127</v>
+        <v>0.0001501072935695707</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.531899804456345e-05</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.000812603648424537</v>
+        <v>3.957783641160839e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003247602918354337</v>
+        <v>0.003010442252809351</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001055015161658695</v>
+        <v>0.0006914188018777162</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>0.0002452036982378336</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002754050471327576</v>
+        <v>0.0007348126013287743</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0009755188579008672</v>
+        <v>0.003197061784137093</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>0.0001735346752050809</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0004053164412604671</v>
+        <v>0.0003089971827608895</v>
       </c>
       <c r="BN8" t="n">
-        <v>-6.680919294495269e-05</v>
+        <v>0.002885907749236372</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0.0002985074626865591</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0006470508901276623</v>
+        <v>0.0006846611735037977</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.683693516699782e-05</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001286857958148399</v>
+        <v>0.0009356079038266685</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0002770448548812587</v>
+        <v>0.0008798506294518726</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001072364649925359</v>
+        <v>0.000479503151137553</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001767227223411436</v>
+        <v>0.001158559611580626</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001510564646646284</v>
+        <v>0.0001081298879729298</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.002827947674603415</v>
+        <v>0.002221354383170621</v>
       </c>
       <c r="BX8" t="n">
-        <v>4.111842105263275e-05</v>
+        <v>5.316767170626957e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0001343283582089516</v>
+        <v>0.000164473684210531</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.683693516701448e-05</v>
+        <v>0.0006806002058121845</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>9.0361445783127e-05</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0009427323109403917</v>
+        <v>0.004291873963515744</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0002733502347591815</v>
+        <v>0.0004275788348476972</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>0.0006308463029587402</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0005855038011438884</v>
+        <v>0.0005587114636855823</v>
       </c>
       <c r="CH8" t="n">
-        <v>9.223782876251752e-05</v>
+        <v>0.000407504612666082</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0001603420630678531</v>
+        <v>0.002802317449216374</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002168994310264896</v>
+        <v>0.001184529654359734</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0008868273452524888</v>
+        <v>0.001047677087675761</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006467661691542259</v>
+        <v>0.00342730790491983</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001669941060903768</v>
+        <v>0.0005756148613291212</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001326699834162515</v>
+        <v>0.00723684210526313</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004221491228070196</v>
+        <v>0.00405701754385962</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008402432283029259</v>
+        <v>0.004715127701375288</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008177445216461743</v>
+        <v>0.007839912280701722</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007367387033399009</v>
+        <v>0.0006633499170812573</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01006876227897843</v>
+        <v>0.001964636542239751</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02035583464154893</v>
+        <v>0.01850746268656719</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0186865671641791</v>
+        <v>0.01894296180010463</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004331140350877205</v>
+        <v>0.01325301204819275</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005746561886051127</v>
+        <v>0.005206286836935225</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00570175438596493</v>
+        <v>0.004660087719298189</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0305372807017544</v>
+        <v>0.0287598944591029</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03401360544217689</v>
+        <v>0.04071166928309783</v>
       </c>
       <c r="R9" t="n">
-        <v>0.006777996070726955</v>
+        <v>0.004854881266490763</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004273084479371336</v>
+        <v>0.003015350877192924</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009036144578313254</v>
+        <v>0.01166226912928758</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01100196463654226</v>
+        <v>0.003164179104477638</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0008349705304518951</v>
+        <v>0.0005344735435596105</v>
       </c>
       <c r="W9" t="n">
-        <v>0.007430664573521717</v>
+        <v>0.01746987951807224</v>
       </c>
       <c r="X9" t="n">
-        <v>0.006304824561403533</v>
+        <v>0.004769736842105243</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002487562189054715</v>
+        <v>0.005301204819277072</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002763957987838572</v>
+        <v>0.007951807228915619</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.008955223880596974</v>
+        <v>0.00945783132530117</v>
       </c>
       <c r="AB9" t="n">
+        <v>0.0003869541182974001</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.005171503957783641</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.01024096385542164</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.006541077969649356</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.004638554216867441</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0008433734939758631</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0009086050240512788</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.005662650602409602</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.005153508771929794</v>
+      </c>
+      <c r="AL9" t="n">
         <v>0.0007186290768380288</v>
       </c>
-      <c r="AC9" t="n">
-        <v>0.00483582089552238</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.007048192771084339</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.008110936682365278</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.006191265892758402</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.0003741314804917018</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.002511773940345385</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.006469298245614053</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.007639979068550518</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.0004934210526315929</v>
-      </c>
       <c r="AM9" t="n">
-        <v>0.001375245579567808</v>
+        <v>0.0002638522427440559</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002929795467108887</v>
+        <v>0.01445783132530118</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.00795395081109369</v>
+        <v>0.006867469879518018</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001779173207744644</v>
+        <v>0.0002946954813359937</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.009397590361445796</v>
+        <v>0.007228915662650571</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.005651491365777106</v>
+        <v>0.004698795180722859</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.006413682522715103</v>
+        <v>0.001817210048102602</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.01359867330016578</v>
+        <v>0.008674698795180702</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.007407407407407374</v>
+        <v>0.0167810026385224</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00262686567164182</v>
+        <v>0.01014925373134331</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003070175438596489</v>
+        <v>0.004864566058595888</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0003316749585406287</v>
+        <v>0.001308215593929851</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.002266445550027629</v>
+        <v>0.003344298245614008</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.009618573797678231</v>
+        <v>0.004960707269155274</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.005546834118262722</v>
+        <v>0.002985074626865691</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.004367053620784944</v>
+        <v>0.003855421686746963</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0009552238805969893</v>
+        <v>0.001096491228070129</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0007367387033399009</v>
+        <v>0.0009823182711199085</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001229289150187052</v>
+        <v>0.0005344735435596215</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.006777996070726966</v>
+        <v>0.004588170259812041</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.003153393907001601</v>
+        <v>0.006388059701492565</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002100608070757315</v>
+        <v>0.001271420674405743</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.006191265892758402</v>
+        <v>0.006029850746268661</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01105583195135429</v>
+        <v>0.006265060240963838</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001260964912280738</v>
+        <v>0.001024096385542128</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.00208955223880597</v>
+        <v>0.008004385964912254</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.00238805970149254</v>
+        <v>0.006447761194029888</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01774461028192374</v>
+        <v>0.01857519788918203</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001480263157894757</v>
+        <v>0.004432717678100251</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.277044854881119e-05</v>
+        <v>0.000164473684210531</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.004469548133595314</v>
+        <v>0.005065963060685985</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.005701754385964941</v>
+        <v>0.005153508771929794</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002210216110019703</v>
+        <v>0.003095632946379201</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01039248203427303</v>
+        <v>0.004116094986807384</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0104477611940298</v>
+        <v>0.001265060240963822</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01145833333333334</v>
+        <v>0.004638554216867441</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0004911591355599709</v>
+        <v>0.000164473684210531</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003673245614035081</v>
+        <v>0.0011608623548922</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0001603420630678642</v>
+        <v>0.001050304035378657</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.00213815789473687</v>
+        <v>0.00148026315789469</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002048192771084334</v>
+        <v>0.006385224274406309</v>
       </c>
       <c r="CD9" t="n">
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001713653952459915</v>
+        <v>0.0008844665561083432</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002093144950287818</v>
+        <v>0.002796833773087071</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.004714912280701778</v>
+        <v>0.00385542168674694</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002487562189054715</v>
+        <v>0.001688654353561991</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0008955223880596774</v>
+        <v>0.006025428413488132</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.004440789473684215</v>
+        <v>0.005963060686015797</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001850746268656711</v>
+        <v>0.008232189973614756</v>
       </c>
     </row>
   </sheetData>
